--- a/wolves_data.xlsx
+++ b/wolves_data.xlsx
@@ -1766,7 +1766,7 @@
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t>makhfi unknown</t>
+          <t>indeterminate</t>
         </is>
       </c>
       <c r="K4" s="0" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t>makhfi unknown</t>
+          <t>indeterminate</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="I11" s="0" t="inlineStr">
         <is>
-          <t>makhfi unknown</t>
+          <t>indeterminate</t>
         </is>
       </c>
       <c r="L11" s="0" t="inlineStr">

--- a/wolves_data.xlsx
+++ b/wolves_data.xlsx
@@ -9186,7 +9186,7 @@
       </c>
       <c r="F70" s="0" t="inlineStr">
         <is>
-          <t>31, omer weiner</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G70" s="0" t="inlineStr">
